--- a/output/excel/invoices.xlsx
+++ b/output/excel/invoices.xlsx
@@ -452,22 +452,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
@@ -552,55 +552,383 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sample_invoice.pdf</t>
+          <t>random_invoice_01_93a0f6.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INV-2024-00842</t>
+          <t>INV-64421</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>PO-9910</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Soylent Corp</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>278 Main St, Chennai, GJ 947258</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>27CDNNU9674Y8Z2</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>CEUYP9285G</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Wayne Enterprises</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>736 Lake Dr, Bengaluru, MH 339082</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2659609.54</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>432068.71</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>3091678.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>PO-9983</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Cyberdyne</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>257 Park Ave, Kolkata, WB 907336</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>35JWPZG2877B4ZZ</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>LBNCQ5618F</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Wayne Enterprises</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>947 Lake Dr, Pune, TS 760167</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1700308.41</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>307880.56</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>2008188.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>2024-12-15</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Bill To:</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>27AABCU9603R1ZX</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>AABCU9603R</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Acme Supplies Pvt. Ltd. XYZ Enterprises Ltd.</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PO-7543</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Initech</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>226 Lake Dr, Chennai, DL 192125</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>01UIPES7955N9ZU</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>TKEZZ9820C</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Goliath National Bank</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>59 Oak Rd, Bengaluru, TS 875535</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2063662.63</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>320199.01</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2383861.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PO-1789</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Globex Inc</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>781 Main St, Mumbai, GJ 796532</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>25YBCPB8032X7Z8</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>FDXNI1420X</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Wayne Enterprises</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>925 Main St, Bengaluru, KA 562938</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2728254.53</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>507682.35</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>3235936.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>PO-2701</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>592 Oak Rd, Mumbai, WB 758677</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>07IQMXU3113A2ZL</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>SRRIM3561U</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Oscorp</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>196 Lake Dr, Mumbai, DL 603413</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2632182.31</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>426673.42</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>3058855.73</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -613,21 +941,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,30 +989,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Tax Amount</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Amount</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Line Total</t>
         </is>
@@ -695,12 +1011,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sample_invoice.pdf</t>
+          <t>random_invoice_01_93a0f6.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INV-2024-00842</t>
+          <t>INV-64421</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -710,43 +1026,49 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Industrial Grade Bolts (M12)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1885.53</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>7,080.00</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>6787.91</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>44498.51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>sample_invoice.pdf</t>
+          <t>random_invoice_01_93a0f6.pdf</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00842</t>
+          <t>INV-64421</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -756,43 +1078,49 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Stainless Steel Nuts (M12)</t>
+          <t>Gadgets</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>4760.73</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>4,720.00</t>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>11997.04</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>54843.61</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>sample_invoice.pdf</t>
+          <t>random_invoice_01_93a0f6.pdf</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>INV-2024-00842</t>
+          <t>INV-64421</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -802,43 +1130,49 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Rubber Gaskets (50mm)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3548.17</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7,840.00</t>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13908.83</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>63583.21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>sample_invoice.pdf</t>
+          <t>random_invoice_01_93a0f6.pdf</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00842</t>
+          <t>INV-64421</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -848,7 +1182,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Packaging &amp; Handling</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -858,21 +1192,7099 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>4262.77</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>39387.99</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>180059.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>191.01</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>733.48</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6845.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>728.53</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>3147.25</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>29374.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>618.88</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>556.99</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3651.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2147.86</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>10223.81</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>46737.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3921.21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2823.27</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26350.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>4166.18</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>6749.21</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>44244.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>941.13</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8169.01</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>37344.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2473.64</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>9498.78</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>88655.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3674.49</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12346.29</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>56440.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>4923.26</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>31705.79</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>144940.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4855.61</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37582.42</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>246373.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>385.52</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>277.57</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2590.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4994.15</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11486.55</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>241217.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>354.26</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>1721.70</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>11286.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4003.69</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13692.62</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>89762.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>4985.95</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>34103.90</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>223570.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4248.93</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5098.72</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>47588.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>1797.23</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>4133.63</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>86806.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>351.86</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1203.36</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7888.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>4587.44</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>8716.14</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>183038.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>55.34</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>216.93</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>991.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>2493.55</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>12567.49</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>117296.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4037.32</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10658.52</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>99479.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_01_93a0f6.pdf</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>INV-64421</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>1828.41</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>457.10</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>9599.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2816.93</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>590.00</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>8619.81</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>56507.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2199.76</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2111.77</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>19709.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>215.83</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>336.69</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3142.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>3075.52</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>6889.16</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>31493.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>197.43</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>189.53</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1768.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>17.48</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>94.39</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>880.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2273.29</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>4910.31</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>45829.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>4407.47</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>17453.58</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>114417.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2774.36</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>3329.23</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>69913.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1739.41</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>8766.63</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>40076.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>756.31</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>4658.87</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>21297.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>4227.90</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>2959.53</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>62150.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2343.00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>8856.54</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>58059.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1518.97</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>1063.28</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>22328.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1815.90</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1089.54</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>10169.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1624.42</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>2046.77</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>13417.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>553.29</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>1195.11</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>7834.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>3375.62</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>23089.24</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>151362.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2871.08</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>574.22</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>12058.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1282.96</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>192.44</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>4041.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2792.66</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2094.49</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>43984.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>4473.38</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>51354.40</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>234762.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>46.31</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>141.71</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>928.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>1892.74</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>23318.56</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>106599.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>4601.69</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>14357.27</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>134001.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>82.81</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>685.67</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>4494.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1876.31</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>93.82</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>1970.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_02_51a956.pdf</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>INV-34040</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>4415.96</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>17487.20</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>114638.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2939.61</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>13228.24</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>86718.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>4978.22</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>14934.66</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>139390.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1934.54</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>10678.66</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>99667.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>2061.03</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>12613.50</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>82688.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>4406.56</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>23795.42</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>155992.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>4815.17</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>21957.18</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>204933.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>4451.25</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>19941.60</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>91161.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>4755.88</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>38522.63</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>252537.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>744.35</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>5627.29</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>36889.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>976.69</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>3555.15</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>16252.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>4924.42</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>4431.98</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>29054.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>856.67</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>428.33</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>8995.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1842.88</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2211.46</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>20640.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>1275.21</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>17495.88</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>79981.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1164.57</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>4891.19</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>45651.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>525.39</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>1450.08</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>13534.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>4805.76</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>10957.13</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>102266.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>24.90</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>65.74</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>613.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1737.38</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>10945.49</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>71753.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>4538.96</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>2451.04</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>16067.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>4810.51</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>12699.75</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>118530.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>64.03</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>299.66</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>2796.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>3759.00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>3157.56</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>29470.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>1091.89</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>6027.23</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>56254.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>3428.25</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>17278.38</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>161264.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>1373.69</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>10632.36</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>69701.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2123.44</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>14906.55</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>97720.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_03_cb1d0f.pdf</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>INV-29895</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>660.63</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>7029.10</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>32133.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>4006.10</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2603.97</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>54683.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>3318.88</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>11151.44</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>50978.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2879.94</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>19698.79</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>129136.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>3252.47</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>22767.29</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>104079.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2794.41</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>3493.01</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>73353.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>4993.05</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>60116.32</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>274817.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1666.72</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>6000.19</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>39334.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>527.80</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>2660.11</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>24827.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>826.42</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>595.02</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>3900.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>569.25</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>478.17</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>2185.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2456.71</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>6485.71</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>60533.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>3127.06</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>3377.22</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>22139.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>4534.86</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>25304.52</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>165885.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>1504.93</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>2708.87</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>17758.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>508.74</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2106.18</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>13807.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>4650.81</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>61204.66</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>279792.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>813.63</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>4686.51</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>43740.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>2129.36</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>1597.02</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>33537.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1753.29</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>21109.61</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>96501.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>4245.48</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>33284.56</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>152158.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>919.24</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>1323.71</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>8677.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>4826.57</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>2702.88</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>12356.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2487.71</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>22389.39</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>146774.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>4889.32</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>25522.25</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>167312.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>142.28</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>256.10</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2390.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>3983.23</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>8962.27</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>188207.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>4314.46</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>28993.17</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>132540.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_04_11cdae.pdf</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>INV-98000</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>2671.69</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>12182.91</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>113707.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>4629.38</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>55737.74</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>254801.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>1700.24</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>2652.37</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>24755.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>4928.66</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>28980.52</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>270484.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>4368.46</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>25162.33</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>234848.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>2018.43</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>6781.92</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>63297.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>3389.35</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>14641.99</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>95986.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>4879.35</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>57381.16</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>262313.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>1260.57</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>882.40</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>18530.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>3164.67</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>5696.41</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>53166.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>4655.70</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>22626.70</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>148330.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>3548.49</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>4613.04</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>96873.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>1301.45</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>4997.57</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>46643.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>2737.98</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>9199.61</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>42055.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>4650.79</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>20928.56</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>137198.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>650.25</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>234.09</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2184.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>3549.33</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>11073.91</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>103356.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>3190.09</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>3987.61</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>83739.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>1646.27</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>1810.90</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>38028.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>3961.63</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>28840.67</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>131843.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>2729.60</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>14739.84</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>96627.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>3096.44</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>4025.37</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>84532.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>1617.95</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>80.90</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>1698.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>2914.76</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>3060.50</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>64270.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Software License</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>862.93</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>647.20</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>13591.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Gadgets</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1393.30</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>9780.97</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>64119.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>576.33</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>6454.90</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>29508.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>4349.36</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>19572.12</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>128306.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>random_invoice_05_376e89.pdf</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>INV-43687</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Server Hosting</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>3039.72</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>5957.85</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>27235.89</t>
         </is>
       </c>
     </row>

--- a/output/excel/invoices.xlsx
+++ b/output/excel/invoices.xlsx
@@ -452,24 +452,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,40 +508,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Vendor GSTIN</t>
+          <t>Buyer Name</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Vendor PAN</t>
+          <t>Buyer Address</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Buyer Name</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Buyer Address</t>
+          <t>Subtotal</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Tax Amount</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Amount</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -552,418 +540,267 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>Due after 30 days</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>PO-5772</t>
+          <t>BPXPO-00536</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Weyland-Yutani Corp</t>
+          <t>Bioplex</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>363 Market Blvd, Bengaluru, TX 213504</t>
+          <t>5 Rue Bader, Narbonne, Aude, 11100</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>19KJVJJ4231Z9ZX</t>
+          <t>Roger Bigot</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RRXPG4535H</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Wayne Enterprises</t>
-        </is>
-      </c>
+          <t>bonbono, 4 Rue des Cites, Aubervilliers, Seine-Saint-Denis, 93300</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>962 Lake Dr, Delhi, GJ 177710</t>
+          <t>5964.50</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Rs.</t>
+          <t>596.45</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>238494.59</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>27100.88</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>265595.47</t>
+          <t>6610.95</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>invoice_02_8e1a46_with_discount.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-80140</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>PO-7863</t>
-        </is>
-      </c>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Due 30 days after receipt</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Umbrella Corp</t>
+          <t>Zencorporations</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>559 5th Avenue, Mumbai, TX 542956</t>
+          <t>Thomas-Mann-Strasse 38, Bonn, 53111</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>07UIDYA8867H4Z8</t>
+          <t>La Galerie</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>MXANJ4634E</t>
+          <t>4 Rue Courtois, Lille, Nord, 59000</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Nakatomi Trading</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>110 Market Blvd, Frankfurt, MH 416714</t>
+          <t>2553.91</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Rs.</t>
+          <t>255.39</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>126783.47</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>23484.18</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>150267.65</t>
+          <t>2809.30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>INV-83837</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>PO-2127</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Soylent Industries</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>969 Main St, London, CA 177171</t>
-        </is>
-      </c>
+          <t>external_3.pdf</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Dunder Mifflin Paper</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>378 5th Avenue, New York, GJ 925631</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>910856.01</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>168811.29</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1079667.30</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_4.pdf</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Acme Corp</t>
+          <t>Neid</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>276 Park Ave, Chennai, CA 616238</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Stark Industries</t>
-        </is>
-      </c>
+          <t>Gillitzerstrasse 10, Rosenheim, BY, 83022</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Obacht AG</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Heidelberger Strasse 86, Bensheim, HE, 64625</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>705 Hill Rd, Hyderabad, CA 931557</t>
+          <t>187700.00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>252304.64</t>
+          <t>18770.00</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>213470.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_5.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>NP#00183</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Initech Ltd</t>
+          <t>notapino</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>583 Park Ave, Pune, NY 360804</t>
+          <t>Ria de Goa 1, Amadora, Lisbon, 2720-059</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07SVEGX7666N8ZY</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
+          <t>Actoonda</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Rua Godinho 634, Matosinhos, Porto, 4450-147</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Goliath National Bank</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>618 Market Blvd, Pune, WB 882487</t>
+          <t>60450.00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Rs.</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>352122.86</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>50120.25</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>402243.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>INV-82593</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>PO-9411</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Cyberdyne Systems</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>980 Market Blvd, Delhi, WB 859341</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>23IKOYW8999A1ZE</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>OIDVZ2104V</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Wayne Enterprises</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>611 Hill Rd, Singapore, NY 479424</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Rs.</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>193793.22</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>24450.18</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>218243.40</t>
+          <t>60450.00</t>
         </is>
       </c>
     </row>
@@ -978,24 +815,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1036,41 +866,6 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Disc. %</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Tax Amount</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CGST %</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>CGST Amt</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>SGST %</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>SGST Amt</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>Line Total</t>
         </is>
       </c>
@@ -1078,12 +873,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1093,62 +888,35 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bulk Widgets</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>9659</t>
-        </is>
-      </c>
+          <t>Dextromethorphan polistirex BPXPN-00057</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Rs.1942.92</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Rs.4371.57</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Rs.4371.57</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Rs.57316.14</t>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>124.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1158,62 +926,35 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Training Sessions</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
+          <t>Venlafaxine Hydrochloride BPXPN-00012</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Rs.3811.05</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Rs.2096.08</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Rs.2096.08</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Rs.88035.26</t>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>400.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1223,62 +964,35 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Security Audit</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
+          <t>Metoclopramide Hydrochloride (BPXPO-00537) BPXPN-00002</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Rs.4563.47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Rs.2464.27</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Rs.2464.27</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Rs.59690.19</t>
+          <t>9.99</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>249.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1288,62 +1002,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Consulting Services</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>8732</t>
-        </is>
-      </c>
+          <t>Avobenzone, octinoxate (BPXPO-00538) BPXPN-00027</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Rs.902.95</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Rs.1381.51</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Rs.1381.51</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Rs.18113.18</t>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>44.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>invoice_01_38b205_split_gst.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>INV-53363</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1353,528 +1040,349 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cloud Server Hosting</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3359</t>
-        </is>
-      </c>
+          <t>Verapamil hydrochloride BPXPN-00066</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Rs.1198.89</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Rs.3237.00</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Rs.3237.00</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Rs.42440.71</t>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>78.90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>invoice_02_8e1a46_with_discount.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>INV-80140</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>UPS Maintenance</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>8201</t>
-        </is>
-      </c>
+          <t>Tiagabine hydrochloride BPXPN-00017</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Rs.708.12</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Rs.198.27</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Rs.906.39</t>
+          <t>153.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>invoice_02_8e1a46_with_discount.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INV-80140</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Logistics &amp; Freight</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5982</t>
-        </is>
-      </c>
+          <t>Ziprasidone hydrochloride (BPXPO-00537) BPXPN-00044</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Rs.2709.80</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Rs.14340.26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Rs.65555.48</t>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>invoice_02_8e1a46_with_discount.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>INV-80140</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Data Storage (1 TB)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
+          <t>Risperidone BPXPN-00023</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Rs.596.32</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Rs.26.83</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Rs.563.52</t>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>invoice_02_8e1a46_with_discount.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INV-80140</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cloud Server Hosting</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6908</t>
-        </is>
-      </c>
+          <t>Metoprolol succinate BPXPN-00067</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Rs.2173.20</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Rs.8918.81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Rs.83242.25</t>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Legal Advisory</t>
+          <t>Acetaminophen BPXPN-00045</t>
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>€2595.82</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>€2569.86</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>€31123.88</t>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Training Sessions</t>
+          <t>Sorafenib BPXPN-00018</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>€4472.97</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>€24154.04</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>€158343.14</t>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>240.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Legal Advisory</t>
+          <t>Telmisartan BPXPN-00022</t>
         </is>
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>€4641.77</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>€35927.30</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>€235523.41</t>
+          <t>9.99</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>149.85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Technical Support</t>
+          <t>Famotidine BPXPN-00068</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>€4145.97</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>€18656.86</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>€225955.36</t>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66.75</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Software License (Annual)</t>
+          <t>Methylphenidate Hydrochloride BPXPN-00005</t>
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
@@ -1885,1087 +1393,2100 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>€1981.14</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>€8320.79</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>€38037.89</t>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>118.35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Software License (Annual)</t>
+          <t>Ibuprofen (BPXPO-00538) BPXPN-00052</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>€1621.08</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>€18610.00</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>€85074.28</t>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>99.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Network Hardware</t>
+          <t>Metformin Hydrochloride (BPXPO-00538) BPXPN-00046</t>
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>€4897.54</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>€52109.83</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>€238216.35</t>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>32.25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Bulk Widgets</t>
+          <t>Avobenzone, Octisalate and Octocrylene BPXPN-00069</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>€2350.26</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>€3807.42</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>€46112.10</t>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>254.85</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Security Audit</t>
+          <t>Carisoprodol BPXPN-00070</t>
         </is>
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>€4589.33</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>€1285.01</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>€5874.34</t>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>invoice_03_b8a13c_international.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INV-83837</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Equipment Rental</t>
+          <t>Losartan Potassium BPXPN-00047</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>€293.57</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>€3370.18</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>€15406.55</t>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Pentazocine Hydrochloride and Naloxone Hydrochloride BPXPN-00051</t>
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>$2702.15</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>$59447.30</t>
+          <t>34.99</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>349.90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Logistics &amp; Freight</t>
+          <t>Omeprazole BPXPN-00071</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>$2122.76</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>$78542.12</t>
+          <t>9.99</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>249.75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Network Hardware</t>
+          <t>Losartan Potassium BPXPN-00019</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>$4404.62</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>$61664.68</t>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>111.25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>Saline BPXPN-00048</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>$2792.97</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>$44687.52</t>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>78.90</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>invoice_04_b91641_minimal.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>INV-68691</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Software License (Annual)</t>
+          <t>Titanium dioxide BPXPN-00021</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>$612.54</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>$7963.02</t>
+          <t>10.25</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>256.25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Legal Advisory</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>9645</t>
-        </is>
-      </c>
+          <t>Bicalutamide (BPXPO-00538) BPXPN-00049</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Rs.1151.08</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Rs.1611.51</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Rs.7366.91</t>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>53.75</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Security Audit</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>9207</t>
-        </is>
-      </c>
+          <t>Ampicillin sodium BPXPN-00050</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Rs.3669.87</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>Rs.11009.61</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>Rs.102756.36</t>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>254.85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4053</t>
-        </is>
-      </c>
+          <t>Octinoxate, Titanium Dioxide, Octisalate BPXPN-00004</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Rs.1848.70</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Rs.7986.38</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Rs.96723.98</t>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>186.75</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_1.pdf</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>BPXINV-00550</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Equipment Rental</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1719</t>
-        </is>
-      </c>
+          <t>Cavia porcellus hair and cavia porcellus skin BPXPN-00020</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Rs.2831.86</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Rs.3681.42</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>Rs.77309.78</t>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>311.25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>invoice_05_5910d5_no_po_no_pan.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>INV-13979</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Equipment Rental</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
+          <t>Glossostigma</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Rs.2635.85</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Rs.25831.33</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Rs.118086.08</t>
+          <t>9.90</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>29.70</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>INV-82593</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Security Audit</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>8886</t>
-        </is>
-      </c>
+          <t>Bayberry</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Rs.1388.54</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Rs.12246.92</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>Rs.80285.38</t>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>1,207.68</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>INV-82593</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Technical Support</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>8816</t>
-        </is>
-      </c>
+          <t>Waxflower</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Rs.3741.31</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Rs.1346.87</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Rs.8829.49</t>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>56.78</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>INV-82593</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Legal Advisory</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
+          <t>Carolina Geranium</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Rs.1462.49</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>Rs.7370.95</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>Rs.68795.53</t>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>187.65</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>INV-82593</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Equipment Rental</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>2342</t>
-        </is>
-      </c>
+          <t>Smooth Solomon's Seal</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Rs.2162.54</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Rs.2595.05</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Rs.54496.01</t>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>14.91</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>invoice_06_7c499d_standard_gst.pdf</t>
+          <t>external_2.pdf</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>INV-82593</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>El Yunque Colorado</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>9.97</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>229.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>external_2.pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Queen Anne's Lace</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>193.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>external_2.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Alaskan Douglasia</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>531.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>external_2.pdf</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Deer Sedge</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>87.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>external_2.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Indian Tobacco</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>14.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Chrysler/300M (Country of origin: France, Color: Blue)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>762-88-0358</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>45400</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>45400</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz/SL-Class (Country of origin: Italy, Color: Red)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>630-35-4784</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>12100</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Audi/90 (Country of origin: Spain, Color: Black)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>582-33-2563</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>18100</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>18100</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ford/Bronco (Country of origin: Spain, Color: Blue)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>877-84-8130</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>30900</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>30900</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Training Sessions</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Audi/A6 (Country of origin: France, Color: Red)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>638-13-7553</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>30800</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>30800</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Mitsubishi/Eclipse (Country of origin: Spain, Color: Silver)</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>771-81-4708</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>external_4.pdf</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Hummer/H1 (Country of origin: Germany, Color: Silver)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>694-41-6257</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>27500</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>27500</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Skid-Steer</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>822-79-9581</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Rs.989.32</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Rs.890.39</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>Rs.5836.99</t>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Backhoe I</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>598-31-5899</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Dump Truck I</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>745-73-2437</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Trencher I</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>813-54-6535</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Grader</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>113-98-4866</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Dump Truck II</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>396-33-2044</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Bulldozer I</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>511-90-9749</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Scraper I</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>307-74-6395</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Compactor I</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>411-71-1752</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Scraper II</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>595-54-0567</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Crawler I</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>573-48-1966</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Compactor II</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>133-65-5977</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Crawler II</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>264-31-6025</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Backhoe II</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>641-82-4321</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Dragline</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>280-60-7659</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Trencher II</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>398-88-4914</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Backhoe III</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>777-92-0504</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Bulldozer II</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>118-37-9226</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Crawler III</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>462-89-9620</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Bulldozer III</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>134-85-7410</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>external_5.pdf</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>NP#00183</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Trencher III</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>317-76-2964</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>2700</t>
         </is>
       </c>
     </row>
